--- a/Results_experiment/exp_2/preds_1111113333322222.xlsx
+++ b/Results_experiment/exp_2/preds_1111113333322222.xlsx
@@ -990,7 +990,7 @@
         <v>1.200000047683716</v>
       </c>
       <c r="D2">
-        <v>0.007129579782485962</v>
+        <v>0.7628300189971924</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1004,7 +1004,7 @@
         <v>4.5</v>
       </c>
       <c r="D3">
-        <v>-0.009084075689315796</v>
+        <v>0.2142972052097321</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1018,7 +1018,7 @@
         <v>-4.099999904632568</v>
       </c>
       <c r="D4">
-        <v>-2.50982141494751</v>
+        <v>-1.907902836799622</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1032,7 +1032,7 @@
         <v>-4.900000095367432</v>
       </c>
       <c r="D5">
-        <v>-1.722351431846619</v>
+        <v>-1.882728219032288</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1046,7 +1046,7 @@
         <v>-5.199999809265137</v>
       </c>
       <c r="D6">
-        <v>-3.743996620178223</v>
+        <v>-1.507186412811279</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1060,7 +1060,7 @@
         <v>-1.299999952316284</v>
       </c>
       <c r="D7">
-        <v>1.04404616355896</v>
+        <v>1.375440835952759</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1074,7 +1074,7 @@
         <v>-3</v>
       </c>
       <c r="D8">
-        <v>0.9072654247283936</v>
+        <v>0.86298668384552</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -1088,7 +1088,7 @@
         <v>14.10000038146973</v>
       </c>
       <c r="D9">
-        <v>11.71352481842041</v>
+        <v>10.92930603027344</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -1102,7 +1102,7 @@
         <v>7</v>
       </c>
       <c r="D10">
-        <v>1.573865413665771</v>
+        <v>1.792067050933838</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -1116,7 +1116,7 @@
         <v>2.5</v>
       </c>
       <c r="D11">
-        <v>1.866076707839966</v>
+        <v>1.424063682556152</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -1130,7 +1130,7 @@
         <v>2.099999904632568</v>
       </c>
       <c r="D12">
-        <v>2.746087074279785</v>
+        <v>2.315037727355957</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -1144,7 +1144,7 @@
         <v>-3.400000095367432</v>
       </c>
       <c r="D13">
-        <v>-1.309177279472351</v>
+        <v>-1.617830514907837</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -1158,7 +1158,7 @@
         <v>1.100000023841858</v>
       </c>
       <c r="D14">
-        <v>-0.642287015914917</v>
+        <v>-0.8396048545837402</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -1172,7 +1172,7 @@
         <v>6.5</v>
       </c>
       <c r="D15">
-        <v>2.532371282577515</v>
+        <v>2.73394513130188</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -1186,7 +1186,7 @@
         <v>2.400000095367432</v>
       </c>
       <c r="D16">
-        <v>2.819370985031128</v>
+        <v>2.756699085235596</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -1200,7 +1200,7 @@
         <v>-7.599999904632568</v>
       </c>
       <c r="D17">
-        <v>-4.085136413574219</v>
+        <v>-4.454390048980713</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -1214,7 +1214,7 @@
         <v>-2.799999952316284</v>
       </c>
       <c r="D18">
-        <v>2.035468816757202</v>
+        <v>1.946258068084717</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -1228,7 +1228,7 @@
         <v>-13.60000038146973</v>
       </c>
       <c r="D19">
-        <v>-8.565281867980957</v>
+        <v>-7.111566543579102</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -1242,7 +1242,7 @@
         <v>6.300000190734863</v>
       </c>
       <c r="D20">
-        <v>1.06743061542511</v>
+        <v>1.812636852264404</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -1256,7 +1256,7 @@
         <v>4.900000095367432</v>
       </c>
       <c r="D21">
-        <v>0.2566222548484802</v>
+        <v>0.9737917184829712</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -1270,7 +1270,7 @@
         <v>-3.799999952316284</v>
       </c>
       <c r="D22">
-        <v>-2.158137083053589</v>
+        <v>-1.304450154304504</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -1284,7 +1284,7 @@
         <v>-4.900000095367432</v>
       </c>
       <c r="D23">
-        <v>-3.375344038009644</v>
+        <v>-2.766823291778564</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -1298,7 +1298,7 @@
         <v>-1.399999976158142</v>
       </c>
       <c r="D24">
-        <v>-3.359016418457031</v>
+        <v>-3.510201692581177</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -1312,7 +1312,7 @@
         <v>2.599999904632568</v>
       </c>
       <c r="D25">
-        <v>0.1689606904983521</v>
+        <v>0.03465458750724792</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -1326,7 +1326,7 @@
         <v>4.400000095367432</v>
       </c>
       <c r="D26">
-        <v>3.35979700088501</v>
+        <v>3.482169628143311</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -1340,7 +1340,7 @@
         <v>1.399999976158142</v>
       </c>
       <c r="D27">
-        <v>-1.426406741142273</v>
+        <v>-0.4309975802898407</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -1354,7 +1354,7 @@
         <v>-2</v>
       </c>
       <c r="D28">
-        <v>0.9477338790893555</v>
+        <v>0.8812673091888428</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -1368,7 +1368,7 @@
         <v>-1.200000047683716</v>
       </c>
       <c r="D29">
-        <v>-2.183371305465698</v>
+        <v>-1.789819002151489</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -1382,7 +1382,7 @@
         <v>4.300000190734863</v>
       </c>
       <c r="D30">
-        <v>2.772993803024292</v>
+        <v>2.974830865859985</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -1396,7 +1396,7 @@
         <v>1.5</v>
       </c>
       <c r="D31">
-        <v>2.138630628585815</v>
+        <v>2.965178489685059</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -1410,7 +1410,7 @@
         <v>-5.300000190734863</v>
       </c>
       <c r="D32">
-        <v>-3.440268278121948</v>
+        <v>-3.598151206970215</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -1424,7 +1424,7 @@
         <v>2.400000095367432</v>
       </c>
       <c r="D33">
-        <v>2.058709383010864</v>
+        <v>2.283485412597656</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -1438,7 +1438,7 @@
         <v>-10.19999980926514</v>
       </c>
       <c r="D34">
-        <v>-3.46470832824707</v>
+        <v>-3.806244373321533</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -1452,7 +1452,7 @@
         <v>-0.6000000238418579</v>
       </c>
       <c r="D35">
-        <v>-4.852255821228027</v>
+        <v>-3.739137887954712</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -1466,7 +1466,7 @@
         <v>1.200000047683716</v>
       </c>
       <c r="D36">
-        <v>2.947096109390259</v>
+        <v>3.047641515731812</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -1480,7 +1480,7 @@
         <v>3.799999952316284</v>
       </c>
       <c r="D37">
-        <v>2.573426485061646</v>
+        <v>2.164967060089111</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -1494,7 +1494,7 @@
         <v>-3.400000095367432</v>
       </c>
       <c r="D38">
-        <v>-2.885471105575562</v>
+        <v>-2.523856163024902</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -1508,7 +1508,7 @@
         <v>-2.900000095367432</v>
       </c>
       <c r="D39">
-        <v>-0.1093627959489822</v>
+        <v>0.3754294812679291</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -1522,7 +1522,7 @@
         <v>-1</v>
       </c>
       <c r="D40">
-        <v>0.4922077655792236</v>
+        <v>1.560601234436035</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -1536,7 +1536,7 @@
         <v>6.800000190734863</v>
       </c>
       <c r="D41">
-        <v>5.750868797302246</v>
+        <v>5.457490921020508</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -1550,7 +1550,7 @@
         <v>5.099999904632568</v>
       </c>
       <c r="D42">
-        <v>2.38349175453186</v>
+        <v>2.572769641876221</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -1564,7 +1564,7 @@
         <v>3.099999904632568</v>
       </c>
       <c r="D43">
-        <v>2.952775239944458</v>
+        <v>2.758913993835449</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -1578,7 +1578,7 @@
         <v>-0.800000011920929</v>
       </c>
       <c r="D44">
-        <v>-1.818257093429565</v>
+        <v>-1.796302080154419</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -1592,7 +1592,7 @@
         <v>-3.099999904632568</v>
       </c>
       <c r="D45">
-        <v>-2.135530471801758</v>
+        <v>-0.905738353729248</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -1606,7 +1606,7 @@
         <v>-1.700000047683716</v>
       </c>
       <c r="D46">
-        <v>-2.287135362625122</v>
+        <v>-1.575463056564331</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -1620,7 +1620,7 @@
         <v>-19.5</v>
       </c>
       <c r="D47">
-        <v>-16.7714786529541</v>
+        <v>-14.40098285675049</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -1634,7 +1634,7 @@
         <v>-6.099999904632568</v>
       </c>
       <c r="D48">
-        <v>-3.117027997970581</v>
+        <v>-2.273108959197998</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -1648,7 +1648,7 @@
         <v>-2.700000047683716</v>
       </c>
       <c r="D49">
-        <v>-2.498917102813721</v>
+        <v>-2.182210922241211</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -1662,7 +1662,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="D50">
-        <v>-0.03260403871536255</v>
+        <v>0.1796029806137085</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -1676,7 +1676,7 @@
         <v>-10.80000019073486</v>
       </c>
       <c r="D51">
-        <v>-8.112528800964355</v>
+        <v>-10.77673053741455</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -1690,7 +1690,7 @@
         <v>-16.10000038146973</v>
       </c>
       <c r="D52">
-        <v>-11.51885414123535</v>
+        <v>-10.60014247894287</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -1704,7 +1704,7 @@
         <v>-0.2000000029802322</v>
       </c>
       <c r="D53">
-        <v>1.17978572845459</v>
+        <v>0.5412530899047852</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -1718,7 +1718,7 @@
         <v>-6.699999809265137</v>
       </c>
       <c r="D54">
-        <v>-3.599043130874634</v>
+        <v>-3.468060255050659</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -1732,7 +1732,7 @@
         <v>4.900000095367432</v>
       </c>
       <c r="D55">
-        <v>2.144522190093994</v>
+        <v>2.751835346221924</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -1746,7 +1746,7 @@
         <v>-0.699999988079071</v>
       </c>
       <c r="D56">
-        <v>-1.510585308074951</v>
+        <v>-1.650742769241333</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -1760,7 +1760,7 @@
         <v>-3.299999952316284</v>
       </c>
       <c r="D57">
-        <v>-2.951407670974731</v>
+        <v>-1.821348190307617</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -1774,7 +1774,7 @@
         <v>1.600000023841858</v>
       </c>
       <c r="D58">
-        <v>-0.5059705972671509</v>
+        <v>0.5264266729354858</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -1788,7 +1788,7 @@
         <v>2.900000095367432</v>
       </c>
       <c r="D59">
-        <v>2.39483380317688</v>
+        <v>1.771358013153076</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -1802,7 +1802,7 @@
         <v>1.700000047683716</v>
       </c>
       <c r="D60">
-        <v>0.3070106506347656</v>
+        <v>0.2936643064022064</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -1816,7 +1816,7 @@
         <v>-3.900000095367432</v>
       </c>
       <c r="D61">
-        <v>-3.028555631637573</v>
+        <v>-2.116828203201294</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -1830,7 +1830,7 @@
         <v>-1.5</v>
       </c>
       <c r="D62">
-        <v>0.7665899991989136</v>
+        <v>0.9174568653106689</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -1844,7 +1844,7 @@
         <v>4.199999809265137</v>
       </c>
       <c r="D63">
-        <v>0.7385159730911255</v>
+        <v>1.234111547470093</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -1858,7 +1858,7 @@
         <v>-6.400000095367432</v>
       </c>
       <c r="D64">
-        <v>-6.708995819091797</v>
+        <v>-6.603356838226318</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -1872,7 +1872,7 @@
         <v>-3.700000047683716</v>
       </c>
       <c r="D65">
-        <v>-3.366318225860596</v>
+        <v>-3.042164087295532</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -1886,7 +1886,7 @@
         <v>5.599999904632568</v>
       </c>
       <c r="D66">
-        <v>1.698552370071411</v>
+        <v>1.891276359558105</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -1900,7 +1900,7 @@
         <v>-0.699999988079071</v>
       </c>
       <c r="D67">
-        <v>-2.42862343788147</v>
+        <v>-1.331521987915039</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -1914,7 +1914,7 @@
         <v>-6.699999809265137</v>
       </c>
       <c r="D68">
-        <v>-3.253774166107178</v>
+        <v>-3.171978235244751</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -1928,7 +1928,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="D69">
-        <v>1.080835342407227</v>
+        <v>0.7996082305908203</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -1942,7 +1942,7 @@
         <v>-7.199999809265137</v>
       </c>
       <c r="D70">
-        <v>-9.390440940856934</v>
+        <v>-9.268242835998535</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -1956,7 +1956,7 @@
         <v>-3.299999952316284</v>
       </c>
       <c r="D71">
-        <v>-1.71564769744873</v>
+        <v>-2.378756999969482</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -1970,7 +1970,7 @@
         <v>-0.699999988079071</v>
       </c>
       <c r="D72">
-        <v>-1.644512891769409</v>
+        <v>-1.753713011741638</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -1984,7 +1984,7 @@
         <v>12.10000038146973</v>
       </c>
       <c r="D73">
-        <v>-1.941789150238037</v>
+        <v>0.2742809951305389</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -1998,7 +1998,7 @@
         <v>4.199999809265137</v>
       </c>
       <c r="D74">
-        <v>2.624476194381714</v>
+        <v>2.690081119537354</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2012,7 +2012,7 @@
         <v>4.900000095367432</v>
       </c>
       <c r="D75">
-        <v>0.8627505302429199</v>
+        <v>0.9159002304077148</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2026,7 +2026,7 @@
         <v>2.900000095367432</v>
       </c>
       <c r="D76">
-        <v>0.2198425531387329</v>
+        <v>0.3969992697238922</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -2040,7 +2040,7 @@
         <v>5.099999904632568</v>
       </c>
       <c r="D77">
-        <v>1.523428440093994</v>
+        <v>2.400676488876343</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -2054,7 +2054,7 @@
         <v>-3.299999952316284</v>
       </c>
       <c r="D78">
-        <v>-4.023210525512695</v>
+        <v>-2.514213800430298</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -2068,7 +2068,7 @@
         <v>-1.100000023841858</v>
       </c>
       <c r="D79">
-        <v>-2.933303117752075</v>
+        <v>-2.620326519012451</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -2082,7 +2082,7 @@
         <v>-7.300000190734863</v>
       </c>
       <c r="D80">
-        <v>-3.508713960647583</v>
+        <v>-3.670877456665039</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -2096,7 +2096,7 @@
         <v>-0.800000011920929</v>
       </c>
       <c r="D81">
-        <v>-4.480229377746582</v>
+        <v>-4.166543483734131</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -2110,7 +2110,7 @@
         <v>3.700000047683716</v>
       </c>
       <c r="D82">
-        <v>2.561247110366821</v>
+        <v>2.468250274658203</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -2124,7 +2124,7 @@
         <v>9.800000190734863</v>
       </c>
       <c r="D83">
-        <v>3.157332897186279</v>
+        <v>3.668059825897217</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -2138,7 +2138,7 @@
         <v>-7.699999809265137</v>
       </c>
       <c r="D84">
-        <v>-2.098931312561035</v>
+        <v>-1.968960762023926</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -2152,7 +2152,7 @@
         <v>-6.599999904632568</v>
       </c>
       <c r="D85">
-        <v>-6.86021900177002</v>
+        <v>-6.322694301605225</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -2166,7 +2166,7 @@
         <v>-1.100000023841858</v>
       </c>
       <c r="D86">
-        <v>-0.1504815220832825</v>
+        <v>-1.184568285942078</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -2180,7 +2180,7 @@
         <v>-1.299999952316284</v>
       </c>
       <c r="D87">
-        <v>-1.905432462692261</v>
+        <v>0.2205353081226349</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -2194,7 +2194,7 @@
         <v>1.100000023841858</v>
       </c>
       <c r="D88">
-        <v>-2.017323017120361</v>
+        <v>-0.892402172088623</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -2208,7 +2208,7 @@
         <v>0.300000011920929</v>
       </c>
       <c r="D89">
-        <v>2.048373937606812</v>
+        <v>1.891822814941406</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -2222,7 +2222,7 @@
         <v>-2.900000095367432</v>
       </c>
       <c r="D90">
-        <v>-3.554072380065918</v>
+        <v>-3.535472393035889</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -2236,7 +2236,7 @@
         <v>3.099999904632568</v>
       </c>
       <c r="D91">
-        <v>3.694204568862915</v>
+        <v>3.190035104751587</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -2250,7 +2250,7 @@
         <v>-1.200000047683716</v>
       </c>
       <c r="D92">
-        <v>0.8454031944274902</v>
+        <v>0.768728494644165</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -2264,7 +2264,7 @@
         <v>-0.5</v>
       </c>
       <c r="D93">
-        <v>-1.546188592910767</v>
+        <v>-1.07037878036499</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -2278,7 +2278,7 @@
         <v>-3.599999904632568</v>
       </c>
       <c r="D94">
-        <v>-3.55344033241272</v>
+        <v>-3.593283176422119</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -2292,7 +2292,7 @@
         <v>-2.299999952316284</v>
       </c>
       <c r="D95">
-        <v>-1.478248834609985</v>
+        <v>-1.588505268096924</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -2306,7 +2306,7 @@
         <v>5</v>
       </c>
       <c r="D96">
-        <v>1.79286789894104</v>
+        <v>2.035290718078613</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -2320,7 +2320,7 @@
         <v>1.100000023841858</v>
       </c>
       <c r="D97">
-        <v>-1.389692187309265</v>
+        <v>-0.7363482713699341</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -2334,7 +2334,7 @@
         <v>0</v>
       </c>
       <c r="D98">
-        <v>1.517703533172607</v>
+        <v>1.84480619430542</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -2348,7 +2348,7 @@
         <v>-3</v>
       </c>
       <c r="D99">
-        <v>-3.045806169509888</v>
+        <v>-2.155614614486694</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -2362,7 +2362,7 @@
         <v>8.199999809265137</v>
       </c>
       <c r="D100">
-        <v>8.304511070251465</v>
+        <v>6.74039363861084</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -2376,7 +2376,7 @@
         <v>-3.799999952316284</v>
       </c>
       <c r="D101">
-        <v>-0.4740633070468903</v>
+        <v>-1.764146089553833</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -2390,7 +2390,7 @@
         <v>11.69999980926514</v>
       </c>
       <c r="D102">
-        <v>2.377385377883911</v>
+        <v>3.261656045913696</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -2404,7 +2404,7 @@
         <v>-3.099999904632568</v>
       </c>
       <c r="D103">
-        <v>-3.693045377731323</v>
+        <v>-3.425644159317017</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -2418,7 +2418,7 @@
         <v>-2.799999952316284</v>
       </c>
       <c r="D104">
-        <v>-3.97093677520752</v>
+        <v>-3.758826971054077</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -2432,7 +2432,7 @@
         <v>6.699999809265137</v>
       </c>
       <c r="D105">
-        <v>2.553195476531982</v>
+        <v>3.332475662231445</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -2446,7 +2446,7 @@
         <v>3</v>
       </c>
       <c r="D106">
-        <v>0.1779813170433044</v>
+        <v>0.328740268945694</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -2460,7 +2460,7 @@
         <v>1.100000023841858</v>
       </c>
       <c r="D107">
-        <v>2.90971565246582</v>
+        <v>2.408939838409424</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -2474,7 +2474,7 @@
         <v>-1.899999976158142</v>
       </c>
       <c r="D108">
-        <v>1.137800335884094</v>
+        <v>0.9885894060134888</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -2488,7 +2488,7 @@
         <v>3.400000095367432</v>
       </c>
       <c r="D109">
-        <v>2.829230070114136</v>
+        <v>3.512673854827881</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -2502,7 +2502,7 @@
         <v>-31</v>
       </c>
       <c r="D110">
-        <v>-24.07823181152344</v>
+        <v>-21.69422912597656</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -2516,7 +2516,7 @@
         <v>-5</v>
       </c>
       <c r="D111">
-        <v>1.313972234725952</v>
+        <v>0.9139883518218994</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -2530,7 +2530,7 @@
         <v>-12.80000019073486</v>
       </c>
       <c r="D112">
-        <v>-12.09549045562744</v>
+        <v>-12.3983325958252</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -2544,7 +2544,7 @@
         <v>-2.400000095367432</v>
       </c>
       <c r="D113">
-        <v>1.516802072525024</v>
+        <v>1.148536920547485</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -2558,7 +2558,7 @@
         <v>0.8999999761581421</v>
       </c>
       <c r="D114">
-        <v>-1.953432083129883</v>
+        <v>-0.3085229694843292</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -2572,7 +2572,7 @@
         <v>1.299999952316284</v>
       </c>
       <c r="D115">
-        <v>1.903321504592896</v>
+        <v>2.02497673034668</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -2586,7 +2586,7 @@
         <v>4.900000095367432</v>
       </c>
       <c r="D116">
-        <v>1.302096009254456</v>
+        <v>1.356052160263062</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -2600,7 +2600,7 @@
         <v>-3</v>
       </c>
       <c r="D117">
-        <v>-0.4071722626686096</v>
+        <v>0.174115389585495</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -2614,7 +2614,7 @@
         <v>7.5</v>
       </c>
       <c r="D118">
-        <v>1.821072340011597</v>
+        <v>2.052066802978516</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -2628,7 +2628,7 @@
         <v>3.900000095367432</v>
       </c>
       <c r="D119">
-        <v>1.177154779434204</v>
+        <v>1.738405227661133</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -2642,7 +2642,7 @@
         <v>3.5</v>
       </c>
       <c r="D120">
-        <v>1.958226919174194</v>
+        <v>1.898787975311279</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -2656,7 +2656,7 @@
         <v>-5.900000095367432</v>
       </c>
       <c r="D121">
-        <v>-1.586181044578552</v>
+        <v>-1.995844602584839</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -2670,7 +2670,7 @@
         <v>6.800000190734863</v>
       </c>
       <c r="D122">
-        <v>2.327056884765625</v>
+        <v>2.526192426681519</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -2684,7 +2684,7 @@
         <v>-2.900000095367432</v>
       </c>
       <c r="D123">
-        <v>-2.482168436050415</v>
+        <v>-1.76635217666626</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -2698,7 +2698,7 @@
         <v>-1.5</v>
       </c>
       <c r="D124">
-        <v>-2.278369426727295</v>
+        <v>-2.407596111297607</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -2712,7 +2712,7 @@
         <v>-5.900000095367432</v>
       </c>
       <c r="D125">
-        <v>-4.056933403015137</v>
+        <v>-4.287769317626953</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -2726,7 +2726,7 @@
         <v>3.799999952316284</v>
       </c>
       <c r="D126">
-        <v>2.709450960159302</v>
+        <v>2.677006483078003</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -2740,7 +2740,7 @@
         <v>11.39999961853027</v>
       </c>
       <c r="D127">
-        <v>7.175388336181641</v>
+        <v>7.385815620422363</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -2754,7 +2754,7 @@
         <v>-20.20000076293945</v>
       </c>
       <c r="D128">
-        <v>-15.69668865203857</v>
+        <v>-12.9565372467041</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -2768,7 +2768,7 @@
         <v>2.799999952316284</v>
       </c>
       <c r="D129">
-        <v>0.8472349643707275</v>
+        <v>0.8988900184631348</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -2782,7 +2782,7 @@
         <v>0.4000000059604645</v>
       </c>
       <c r="D130">
-        <v>1.626665949821472</v>
+        <v>1.455719828605652</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -2796,7 +2796,7 @@
         <v>0.6000000238418579</v>
       </c>
       <c r="D131">
-        <v>1.728683233261108</v>
+        <v>1.673093438148499</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -2810,7 +2810,7 @@
         <v>-5.400000095367432</v>
       </c>
       <c r="D132">
-        <v>-0.4536804556846619</v>
+        <v>-1.160888075828552</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -2824,7 +2824,7 @@
         <v>1.600000023841858</v>
       </c>
       <c r="D133">
-        <v>-0.004037618637084961</v>
+        <v>0.6033147573471069</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -2838,7 +2838,7 @@
         <v>-6.300000190734863</v>
       </c>
       <c r="D134">
-        <v>5.712333679199219</v>
+        <v>2.991798639297485</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -2852,7 +2852,7 @@
         <v>3.900000095367432</v>
       </c>
       <c r="D135">
-        <v>2.404576539993286</v>
+        <v>2.707154273986816</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -2866,7 +2866,7 @@
         <v>-10.80000019073486</v>
       </c>
       <c r="D136">
-        <v>-6.94650936126709</v>
+        <v>-5.350724697113037</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -2880,7 +2880,7 @@
         <v>-6.300000190734863</v>
       </c>
       <c r="D137">
-        <v>-0.5840044617652893</v>
+        <v>0.7353430986404419</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -2894,7 +2894,7 @@
         <v>-9.300000190734863</v>
       </c>
       <c r="D138">
-        <v>-6.642189979553223</v>
+        <v>-5.527713775634766</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -2908,7 +2908,7 @@
         <v>-32.20000076293945</v>
       </c>
       <c r="D139">
-        <v>-24.13398551940918</v>
+        <v>-22.45938491821289</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -2922,7 +2922,7 @@
         <v>-0.800000011920929</v>
       </c>
       <c r="D140">
-        <v>2.069700956344604</v>
+        <v>1.979670524597168</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -2936,7 +2936,7 @@
         <v>-6.900000095367432</v>
       </c>
       <c r="D141">
-        <v>-5.25702953338623</v>
+        <v>-5.294856548309326</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -2950,7 +2950,7 @@
         <v>0.6000000238418579</v>
       </c>
       <c r="D142">
-        <v>-0.584094226360321</v>
+        <v>0.2363878190517426</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -2964,7 +2964,7 @@
         <v>-0.4000000059604645</v>
       </c>
       <c r="D143">
-        <v>1.650841951370239</v>
+        <v>2.110201120376587</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -2978,7 +2978,7 @@
         <v>-3.200000047683716</v>
       </c>
       <c r="D144">
-        <v>-1.761780381202698</v>
+        <v>-1.036211848258972</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -2992,7 +2992,7 @@
         <v>0.4000000059604645</v>
       </c>
       <c r="D145">
-        <v>1.564015984535217</v>
+        <v>1.222511529922485</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3006,7 +3006,7 @@
         <v>-23.20000076293945</v>
       </c>
       <c r="D146">
-        <v>-19.90373229980469</v>
+        <v>-20.07287216186523</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3020,7 +3020,7 @@
         <v>-6.099999904632568</v>
       </c>
       <c r="D147">
-        <v>-3.113710165023804</v>
+        <v>-3.121060132980347</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -3034,7 +3034,7 @@
         <v>-2.099999904632568</v>
       </c>
       <c r="D148">
-        <v>-0.9553928375244141</v>
+        <v>-0.8910427093505859</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -3048,7 +3048,7 @@
         <v>-2</v>
       </c>
       <c r="D149">
-        <v>-3.42849326133728</v>
+        <v>-3.379624366760254</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -3062,7 +3062,7 @@
         <v>-3.099999904632568</v>
       </c>
       <c r="D150">
-        <v>-0.6548861861228943</v>
+        <v>0.234706312417984</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -3076,7 +3076,7 @@
         <v>5.5</v>
       </c>
       <c r="D151">
-        <v>1.410206079483032</v>
+        <v>1.002335667610168</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -3090,7 +3090,7 @@
         <v>4</v>
       </c>
       <c r="D152">
-        <v>2.604862928390503</v>
+        <v>2.88771653175354</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -3104,7 +3104,7 @@
         <v>3.400000095367432</v>
       </c>
       <c r="D153">
-        <v>2.695011854171753</v>
+        <v>2.323899269104004</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -3118,7 +3118,7 @@
         <v>-4.400000095367432</v>
       </c>
       <c r="D154">
-        <v>-3.741685152053833</v>
+        <v>-3.199619770050049</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -3132,7 +3132,7 @@
         <v>-0.300000011920929</v>
       </c>
       <c r="D155">
-        <v>-2.181215286254883</v>
+        <v>-3.208758354187012</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -3146,7 +3146,7 @@
         <v>4.800000190734863</v>
       </c>
       <c r="D156">
-        <v>2.35591459274292</v>
+        <v>2.232532024383545</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -3160,7 +3160,7 @@
         <v>-8.399999618530273</v>
       </c>
       <c r="D157">
-        <v>-9.713629722595215</v>
+        <v>-10.27065849304199</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -3174,7 +3174,7 @@
         <v>0.2000000029802322</v>
       </c>
       <c r="D158">
-        <v>-3.258837699890137</v>
+        <v>-3.197576761245728</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -3188,7 +3188,7 @@
         <v>2.200000047683716</v>
       </c>
       <c r="D159">
-        <v>1.826358079910278</v>
+        <v>1.489526867866516</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -3202,7 +3202,7 @@
         <v>-3.5</v>
       </c>
       <c r="D160">
-        <v>-2.700323581695557</v>
+        <v>-3.25607442855835</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -3216,7 +3216,7 @@
         <v>1.799999952316284</v>
       </c>
       <c r="D161">
-        <v>2.168316125869751</v>
+        <v>1.387784242630005</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -3230,7 +3230,7 @@
         <v>3.5</v>
       </c>
       <c r="D162">
-        <v>2.368636608123779</v>
+        <v>2.413601636886597</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -3244,7 +3244,7 @@
         <v>2.400000095367432</v>
       </c>
       <c r="D163">
-        <v>1.491907119750977</v>
+        <v>2.079954147338867</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -3258,7 +3258,7 @@
         <v>1.5</v>
       </c>
       <c r="D164">
-        <v>-1.402399778366089</v>
+        <v>0.3353848159313202</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -3272,7 +3272,7 @@
         <v>-5.900000095367432</v>
       </c>
       <c r="D165">
-        <v>-13.54606533050537</v>
+        <v>-17.26171684265137</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -3286,7 +3286,7 @@
         <v>-1</v>
       </c>
       <c r="D166">
-        <v>-1.440421104431152</v>
+        <v>-1.417712569236755</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -3300,7 +3300,7 @@
         <v>-1.700000047683716</v>
       </c>
       <c r="D167">
-        <v>2.683012247085571</v>
+        <v>3.495095491409302</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -3314,7 +3314,7 @@
         <v>3.799999952316284</v>
       </c>
       <c r="D168">
-        <v>-0.122523158788681</v>
+        <v>-0.05780099332332611</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -3328,7 +3328,7 @@
         <v>-0.8999999761581421</v>
       </c>
       <c r="D169">
-        <v>1.084730744361877</v>
+        <v>0.7209562063217163</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -3342,7 +3342,7 @@
         <v>0.6000000238418579</v>
       </c>
       <c r="D170">
-        <v>-1.557826519012451</v>
+        <v>-1.548140645027161</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -3356,7 +3356,7 @@
         <v>-1.299999952316284</v>
       </c>
       <c r="D171">
-        <v>1.141392111778259</v>
+        <v>1.017374277114868</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -3370,7 +3370,7 @@
         <v>-1.600000023841858</v>
       </c>
       <c r="D172">
-        <v>2.35332179069519</v>
+        <v>1.863473892211914</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -3384,7 +3384,7 @@
         <v>3.5</v>
       </c>
       <c r="D173">
-        <v>-0.3488417863845825</v>
+        <v>0.4437799155712128</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -3398,7 +3398,7 @@
         <v>6.099999904632568</v>
       </c>
       <c r="D174">
-        <v>2.131957292556763</v>
+        <v>2.269472599029541</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -3412,7 +3412,7 @@
         <v>-21.10000038146973</v>
       </c>
       <c r="D175">
-        <v>-11.23147869110107</v>
+        <v>-11.79900169372559</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -3426,7 +3426,7 @@
         <v>-5.5</v>
       </c>
       <c r="D176">
-        <v>-2.652932405471802</v>
+        <v>-1.56011962890625</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -3440,7 +3440,7 @@
         <v>4.300000190734863</v>
       </c>
       <c r="D177">
-        <v>2.055193185806274</v>
+        <v>2.058075428009033</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -3454,7 +3454,7 @@
         <v>5.199999809265137</v>
       </c>
       <c r="D178">
-        <v>0.9298427104949951</v>
+        <v>1.398384571075439</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -3468,7 +3468,7 @@
         <v>-3.400000095367432</v>
       </c>
       <c r="D179">
-        <v>-4.751355171203613</v>
+        <v>-5.302455902099609</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -3482,7 +3482,7 @@
         <v>8.100000381469727</v>
       </c>
       <c r="D180">
-        <v>2.879583120346069</v>
+        <v>3.390475511550903</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -3496,7 +3496,7 @@
         <v>3.200000047683716</v>
       </c>
       <c r="D181">
-        <v>1.487885594367981</v>
+        <v>1.789232492446899</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -3510,7 +3510,7 @@
         <v>-1</v>
       </c>
       <c r="D182">
-        <v>-1.78636622428894</v>
+        <v>-0.9703385829925537</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -3524,7 +3524,7 @@
         <v>-13.30000019073486</v>
       </c>
       <c r="D183">
-        <v>-7.259581565856934</v>
+        <v>-6.394223213195801</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -3538,7 +3538,7 @@
         <v>-1.299999952316284</v>
       </c>
       <c r="D184">
-        <v>1.408902287483215</v>
+        <v>1.38094687461853</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -3552,7 +3552,7 @@
         <v>-7.800000190734863</v>
       </c>
       <c r="D185">
-        <v>-3.197806835174561</v>
+        <v>-3.228556871414185</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -3566,7 +3566,7 @@
         <v>-4.900000095367432</v>
       </c>
       <c r="D186">
-        <v>-3.466696977615356</v>
+        <v>-3.037304401397705</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -3580,7 +3580,7 @@
         <v>0.5</v>
       </c>
       <c r="D187">
-        <v>-2.991521596908569</v>
+        <v>-2.194782733917236</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -3594,7 +3594,7 @@
         <v>-7</v>
       </c>
       <c r="D188">
-        <v>-3.48174262046814</v>
+        <v>-3.693168640136719</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -3608,7 +3608,7 @@
         <v>-1.100000023841858</v>
       </c>
       <c r="D189">
-        <v>-2.733018159866333</v>
+        <v>-2.584033727645874</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -3622,7 +3622,7 @@
         <v>10.19999980926514</v>
       </c>
       <c r="D190">
-        <v>-1.928870797157288</v>
+        <v>0.4315183460712433</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -3636,7 +3636,7 @@
         <v>-4.599999904632568</v>
       </c>
       <c r="D191">
-        <v>-1.7922523021698</v>
+        <v>-2.43952202796936</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -3650,7 +3650,7 @@
         <v>-5.5</v>
       </c>
       <c r="D192">
-        <v>-2.12008810043335</v>
+        <v>-1.626942157745361</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -3664,7 +3664,7 @@
         <v>1.600000023841858</v>
       </c>
       <c r="D193">
-        <v>1.663486480712891</v>
+        <v>1.913243293762207</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -3678,7 +3678,7 @@
         <v>-6.199999809265137</v>
       </c>
       <c r="D194">
-        <v>-1.746647953987122</v>
+        <v>-0.7795740365982056</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -3692,7 +3692,7 @@
         <v>4.599999904632568</v>
       </c>
       <c r="D195">
-        <v>3.181862115859985</v>
+        <v>2.509068489074707</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -3706,7 +3706,7 @@
         <v>-2.700000047683716</v>
       </c>
       <c r="D196">
-        <v>-1.962674379348755</v>
+        <v>-2.235575914382935</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -3720,7 +3720,7 @@
         <v>-11.69999980926514</v>
       </c>
       <c r="D197">
-        <v>-3.954494476318359</v>
+        <v>-4.151960849761963</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -3734,7 +3734,7 @@
         <v>-4.300000190734863</v>
       </c>
       <c r="D198">
-        <v>-0.5433861017227173</v>
+        <v>-0.5261355638504028</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -3748,7 +3748,7 @@
         <v>4.099999904632568</v>
       </c>
       <c r="D199">
-        <v>1.993147134780884</v>
+        <v>2.38654899597168</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -3762,7 +3762,7 @@
         <v>4.699999809265137</v>
       </c>
       <c r="D200">
-        <v>-0.5423036217689514</v>
+        <v>-0.5665799379348755</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -3776,7 +3776,7 @@
         <v>-4.599999904632568</v>
       </c>
       <c r="D201">
-        <v>-0.9788546562194824</v>
+        <v>-0.9891908168792725</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -3790,7 +3790,7 @@
         <v>-25.10000038146973</v>
       </c>
       <c r="D202">
-        <v>-20.14918327331543</v>
+        <v>-16.6056022644043</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -3804,7 +3804,7 @@
         <v>2.299999952316284</v>
       </c>
       <c r="D203">
-        <v>3.130037069320679</v>
+        <v>2.455584526062012</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -3818,7 +3818,7 @@
         <v>-15.60000038146973</v>
       </c>
       <c r="D204">
-        <v>-1.976914882659912</v>
+        <v>-0.5152412056922913</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -3832,7 +3832,7 @@
         <v>-1.200000047683716</v>
       </c>
       <c r="D205">
-        <v>0.09902960062026978</v>
+        <v>0.4746476113796234</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -3846,7 +3846,7 @@
         <v>-20</v>
       </c>
       <c r="D206">
-        <v>-14.46266555786133</v>
+        <v>-15.83702945709229</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -3860,7 +3860,7 @@
         <v>-4.300000190734863</v>
       </c>
       <c r="D207">
-        <v>-1.545024156570435</v>
+        <v>-0.6718587279319763</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -3874,7 +3874,7 @@
         <v>-3.700000047683716</v>
       </c>
       <c r="D208">
-        <v>-3.230029582977295</v>
+        <v>-2.234765291213989</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -3888,7 +3888,7 @@
         <v>-2.5</v>
       </c>
       <c r="D209">
-        <v>1.999634265899658</v>
+        <v>1.991600513458252</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -3902,7 +3902,7 @@
         <v>-0.4000000059604645</v>
       </c>
       <c r="D210">
-        <v>-1.265269041061401</v>
+        <v>-0.9204878807067871</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -3916,7 +3916,7 @@
         <v>-4.199999809265137</v>
       </c>
       <c r="D211">
-        <v>-3.805882215499878</v>
+        <v>-3.536623954772949</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -3930,7 +3930,7 @@
         <v>1</v>
       </c>
       <c r="D212">
-        <v>-2.558834791183472</v>
+        <v>-1.721933722496033</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -3944,7 +3944,7 @@
         <v>-16.60000038146973</v>
       </c>
       <c r="D213">
-        <v>-8.713212013244629</v>
+        <v>-7.741340160369873</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -3958,7 +3958,7 @@
         <v>1.399999976158142</v>
       </c>
       <c r="D214">
-        <v>2.257624626159668</v>
+        <v>2.410716772079468</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -3972,7 +3972,7 @@
         <v>-5.699999809265137</v>
       </c>
       <c r="D215">
-        <v>-2.223617076873779</v>
+        <v>-1.308103084564209</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -3986,7 +3986,7 @@
         <v>7.699999809265137</v>
       </c>
       <c r="D216">
-        <v>2.290203809738159</v>
+        <v>2.000722885131836</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4000,7 +4000,7 @@
         <v>-4.5</v>
       </c>
       <c r="D217">
-        <v>-4.808101654052734</v>
+        <v>-4.073160648345947</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4014,7 +4014,7 @@
         <v>2</v>
       </c>
       <c r="D218">
-        <v>2.337785959243774</v>
+        <v>2.280614376068115</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4028,7 +4028,7 @@
         <v>-4.800000190734863</v>
       </c>
       <c r="D219">
-        <v>-3.52009105682373</v>
+        <v>-3.636151313781738</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -4042,7 +4042,7 @@
         <v>-5</v>
       </c>
       <c r="D220">
-        <v>-0.8838368654251099</v>
+        <v>-0.3344103097915649</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -4056,7 +4056,7 @@
         <v>2.5</v>
       </c>
       <c r="D221">
-        <v>2.627592086791992</v>
+        <v>3.00698709487915</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -4070,7 +4070,7 @@
         <v>-41</v>
       </c>
       <c r="D222">
-        <v>-26.43544960021973</v>
+        <v>-25.21924018859863</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -4084,7 +4084,7 @@
         <v>-5.400000095367432</v>
       </c>
       <c r="D223">
-        <v>-3.37715220451355</v>
+        <v>-2.932214736938477</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -4098,7 +4098,7 @@
         <v>-1.799999952316284</v>
       </c>
       <c r="D224">
-        <v>-2.969801187515259</v>
+        <v>-3.415571928024292</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -4112,7 +4112,7 @@
         <v>-0.1000000014901161</v>
       </c>
       <c r="D225">
-        <v>0.9982631206512451</v>
+        <v>0.412915974855423</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -4126,7 +4126,7 @@
         <v>-1.299999952316284</v>
       </c>
       <c r="D226">
-        <v>0.7240889072418213</v>
+        <v>0.9370658397674561</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -4140,7 +4140,7 @@
         <v>8.100000381469727</v>
       </c>
       <c r="D227">
-        <v>6.295489311218262</v>
+        <v>6.47337532043457</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -4154,7 +4154,7 @@
         <v>-0.4000000059604645</v>
       </c>
       <c r="D228">
-        <v>-0.4924116432666779</v>
+        <v>0.302418977022171</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -4168,7 +4168,7 @@
         <v>-6.300000190734863</v>
       </c>
       <c r="D229">
-        <v>-3.623576402664185</v>
+        <v>-3.723249197006226</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -4182,7 +4182,7 @@
         <v>-1.100000023841858</v>
       </c>
       <c r="D230">
-        <v>-1.539961814880371</v>
+        <v>-0.8999464511871338</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -4196,7 +4196,7 @@
         <v>-5.099999904632568</v>
       </c>
       <c r="D231">
-        <v>-3.08608603477478</v>
+        <v>-2.694072961807251</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -4210,7 +4210,7 @@
         <v>-2.5</v>
       </c>
       <c r="D232">
-        <v>-2.694744348526001</v>
+        <v>-1.385222196578979</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -4224,7 +4224,7 @@
         <v>1.700000047683716</v>
       </c>
       <c r="D233">
-        <v>2.442086219787598</v>
+        <v>2.230093240737915</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -4238,7 +4238,7 @@
         <v>1.700000047683716</v>
       </c>
       <c r="D234">
-        <v>2.046096563339233</v>
+        <v>2.010322332382202</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -4252,7 +4252,7 @@
         <v>-5.699999809265137</v>
       </c>
       <c r="D235">
-        <v>0.6851520538330078</v>
+        <v>-0.1021061837673187</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -4266,7 +4266,7 @@
         <v>3.400000095367432</v>
       </c>
       <c r="D236">
-        <v>-0.08486241102218628</v>
+        <v>-0.1674050837755203</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -4280,7 +4280,7 @@
         <v>6.699999809265137</v>
       </c>
       <c r="D237">
-        <v>0.3600860238075256</v>
+        <v>1.981384038925171</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -4294,7 +4294,7 @@
         <v>-7.199999809265137</v>
       </c>
       <c r="D238">
-        <v>-3.315786123275757</v>
+        <v>-3.306474685668945</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -4308,7 +4308,7 @@
         <v>-4.400000095367432</v>
       </c>
       <c r="D239">
-        <v>0.710975170135498</v>
+        <v>-0.8857375383377075</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -4322,7 +4322,7 @@
         <v>4.099999904632568</v>
       </c>
       <c r="D240">
-        <v>-1.860793709754944</v>
+        <v>-2.139746904373169</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -4336,7 +4336,7 @@
         <v>-0.8999999761581421</v>
       </c>
       <c r="D241">
-        <v>-1.509496331214905</v>
+        <v>-1.316638827323914</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -4350,7 +4350,7 @@
         <v>1.899999976158142</v>
       </c>
       <c r="D242">
-        <v>1.024083614349365</v>
+        <v>0.5031158924102783</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -4364,7 +4364,7 @@
         <v>1.700000047683716</v>
       </c>
       <c r="D243">
-        <v>-1.062154173851013</v>
+        <v>-0.3770093023777008</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -4378,7 +4378,7 @@
         <v>13.60000038146973</v>
       </c>
       <c r="D244">
-        <v>10.82196521759033</v>
+        <v>10.39907932281494</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -4392,7 +4392,7 @@
         <v>3.400000095367432</v>
       </c>
       <c r="D245">
-        <v>1.28620433807373</v>
+        <v>1.821824550628662</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -4406,7 +4406,7 @@
         <v>-14.80000019073486</v>
       </c>
       <c r="D246">
-        <v>-14.60586833953857</v>
+        <v>-12.77885341644287</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -4420,7 +4420,7 @@
         <v>-3.700000047683716</v>
       </c>
       <c r="D247">
-        <v>-1.450211763381958</v>
+        <v>-1.486939787864685</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -4434,7 +4434,7 @@
         <v>-1.299999952316284</v>
       </c>
       <c r="D248">
-        <v>-2.908231019973755</v>
+        <v>-1.96267032623291</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -4448,7 +4448,7 @@
         <v>2</v>
       </c>
       <c r="D249">
-        <v>1.153984069824219</v>
+        <v>1.098882913589478</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -4462,7 +4462,7 @@
         <v>1.399999976158142</v>
       </c>
       <c r="D250">
-        <v>-1.805575132369995</v>
+        <v>-0.8175712823867798</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -4476,7 +4476,7 @@
         <v>-3.5</v>
       </c>
       <c r="D251">
-        <v>-4.129580497741699</v>
+        <v>-1.434026718139648</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -4490,7 +4490,7 @@
         <v>-8.899999618530273</v>
       </c>
       <c r="D252">
-        <v>-3.221550703048706</v>
+        <v>-3.075861930847168</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -4504,7 +4504,7 @@
         <v>1.399999976158142</v>
       </c>
       <c r="D253">
-        <v>0.2222158908843994</v>
+        <v>-0.9355775117874146</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -4518,7 +4518,7 @@
         <v>-15.39999961853027</v>
       </c>
       <c r="D254">
-        <v>-17.43218040466309</v>
+        <v>-18.2819766998291</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -4532,7 +4532,7 @@
         <v>-33.09999847412109</v>
       </c>
       <c r="D255">
-        <v>-28.41739273071289</v>
+        <v>-26.12701416015625</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -4546,7 +4546,7 @@
         <v>-1.600000023841858</v>
       </c>
       <c r="D256">
-        <v>-3.195167303085327</v>
+        <v>-2.879467248916626</v>
       </c>
     </row>
     <row r="257" spans="1:4">
@@ -4560,7 +4560,7 @@
         <v>3.099999904632568</v>
       </c>
       <c r="D257">
-        <v>0.1256142854690552</v>
+        <v>0.4819068014621735</v>
       </c>
     </row>
     <row r="258" spans="1:4">
@@ -4574,7 +4574,7 @@
         <v>0.8999999761581421</v>
       </c>
       <c r="D258">
-        <v>0.1380507349967957</v>
+        <v>0.05882135033607483</v>
       </c>
     </row>
     <row r="259" spans="1:4">
@@ -4588,7 +4588,7 @@
         <v>3.799999952316284</v>
       </c>
       <c r="D259">
-        <v>-1.34962272644043</v>
+        <v>-0.1197008788585663</v>
       </c>
     </row>
     <row r="260" spans="1:4">
@@ -4602,7 +4602,7 @@
         <v>-16.5</v>
       </c>
       <c r="D260">
-        <v>-4.269289970397949</v>
+        <v>-3.967094659805298</v>
       </c>
     </row>
     <row r="261" spans="1:4">
@@ -4616,7 +4616,7 @@
         <v>-5</v>
       </c>
       <c r="D261">
-        <v>-2.374650239944458</v>
+        <v>-2.978957653045654</v>
       </c>
     </row>
     <row r="262" spans="1:4">
@@ -4630,7 +4630,7 @@
         <v>-6</v>
       </c>
       <c r="D262">
-        <v>-3.486469745635986</v>
+        <v>-3.528150320053101</v>
       </c>
     </row>
     <row r="263" spans="1:4">
@@ -4644,7 +4644,7 @@
         <v>-6.300000190734863</v>
       </c>
       <c r="D263">
-        <v>-3.771207332611084</v>
+        <v>-2.940705299377441</v>
       </c>
     </row>
     <row r="264" spans="1:4">
@@ -4658,7 +4658,7 @@
         <v>-3.5</v>
       </c>
       <c r="D264">
-        <v>-1.127342104911804</v>
+        <v>-1.228383421897888</v>
       </c>
     </row>
     <row r="265" spans="1:4">
@@ -4672,7 +4672,7 @@
         <v>-0.1000000014901161</v>
       </c>
       <c r="D265">
-        <v>0.0267452597618103</v>
+        <v>0.04796043038368225</v>
       </c>
     </row>
     <row r="266" spans="1:4">
@@ -4686,7 +4686,7 @@
         <v>-1.299999952316284</v>
       </c>
       <c r="D266">
-        <v>-2.689541339874268</v>
+        <v>-2.960267066955566</v>
       </c>
     </row>
     <row r="267" spans="1:4">
@@ -4700,7 +4700,7 @@
         <v>5.5</v>
       </c>
       <c r="D267">
-        <v>2.741134166717529</v>
+        <v>2.828506469726562</v>
       </c>
     </row>
     <row r="268" spans="1:4">
@@ -4714,7 +4714,7 @@
         <v>-29.20000076293945</v>
       </c>
       <c r="D268">
-        <v>-21.75143432617188</v>
+        <v>-19.28621673583984</v>
       </c>
     </row>
     <row r="269" spans="1:4">
@@ -4728,7 +4728,7 @@
         <v>-2.200000047683716</v>
       </c>
       <c r="D269">
-        <v>-1.515002250671387</v>
+        <v>-1.076227903366089</v>
       </c>
     </row>
     <row r="270" spans="1:4">
@@ -4742,7 +4742,7 @@
         <v>-2.900000095367432</v>
       </c>
       <c r="D270">
-        <v>-3.5274498462677</v>
+        <v>-3.52865195274353</v>
       </c>
     </row>
     <row r="271" spans="1:4">
@@ -4756,7 +4756,7 @@
         <v>-3.799999952316284</v>
       </c>
       <c r="D271">
-        <v>-2.438191175460815</v>
+        <v>-1.217869400978088</v>
       </c>
     </row>
     <row r="272" spans="1:4">
@@ -4770,7 +4770,7 @@
         <v>-10.30000019073486</v>
       </c>
       <c r="D272">
-        <v>-3.148159027099609</v>
+        <v>-3.078672885894775</v>
       </c>
     </row>
     <row r="273" spans="1:4">
@@ -4784,7 +4784,7 @@
         <v>-7.5</v>
       </c>
       <c r="D273">
-        <v>-12.65225887298584</v>
+        <v>-15.38583946228027</v>
       </c>
     </row>
     <row r="274" spans="1:4">
@@ -4798,7 +4798,7 @@
         <v>-3</v>
       </c>
       <c r="D274">
-        <v>-3.570959806442261</v>
+        <v>-3.572080612182617</v>
       </c>
     </row>
     <row r="275" spans="1:4">
@@ -4812,7 +4812,7 @@
         <v>-5.699999809265137</v>
       </c>
       <c r="D275">
-        <v>-2.521270036697388</v>
+        <v>-2.887618064880371</v>
       </c>
     </row>
     <row r="276" spans="1:4">
@@ -4826,7 +4826,7 @@
         <v>3.5</v>
       </c>
       <c r="D276">
-        <v>1.551159024238586</v>
+        <v>1.698978066444397</v>
       </c>
     </row>
     <row r="277" spans="1:4">
@@ -4840,7 +4840,7 @@
         <v>0.4000000059604645</v>
       </c>
       <c r="D277">
-        <v>-1.413151741027832</v>
+        <v>-1.249396204948425</v>
       </c>
     </row>
     <row r="278" spans="1:4">
@@ -4854,7 +4854,7 @@
         <v>3.5</v>
       </c>
       <c r="D278">
-        <v>2.121748208999634</v>
+        <v>2.296055555343628</v>
       </c>
     </row>
     <row r="279" spans="1:4">
@@ -4868,7 +4868,7 @@
         <v>-31.29999923706055</v>
       </c>
       <c r="D279">
-        <v>-24.14923667907715</v>
+        <v>-21.4317626953125</v>
       </c>
     </row>
     <row r="280" spans="1:4">
@@ -4882,7 +4882,7 @@
         <v>-0.6000000238418579</v>
       </c>
       <c r="D280">
-        <v>0.9323050975799561</v>
+        <v>1.19010329246521</v>
       </c>
     </row>
     <row r="281" spans="1:4">
@@ -4896,7 +4896,7 @@
         <v>2</v>
       </c>
       <c r="D281">
-        <v>0.8124037981033325</v>
+        <v>0.5205405950546265</v>
       </c>
     </row>
     <row r="282" spans="1:4">
@@ -4910,7 +4910,7 @@
         <v>1</v>
       </c>
       <c r="D282">
-        <v>-3.379425287246704</v>
+        <v>-2.157129049301147</v>
       </c>
     </row>
     <row r="283" spans="1:4">
@@ -4924,7 +4924,7 @@
         <v>-5.199999809265137</v>
       </c>
       <c r="D283">
-        <v>-2.735294103622437</v>
+        <v>-2.767948150634766</v>
       </c>
     </row>
     <row r="284" spans="1:4">
@@ -4938,7 +4938,7 @@
         <v>-0.300000011920929</v>
       </c>
       <c r="D284">
-        <v>-0.666404664516449</v>
+        <v>-0.7925411462783813</v>
       </c>
     </row>
     <row r="285" spans="1:4">
@@ -4952,7 +4952,7 @@
         <v>2.900000095367432</v>
       </c>
       <c r="D285">
-        <v>2.452711343765259</v>
+        <v>2.65222692489624</v>
       </c>
     </row>
     <row r="286" spans="1:4">
@@ -4966,7 +4966,7 @@
         <v>1.700000047683716</v>
       </c>
       <c r="D286">
-        <v>-0.4600204825401306</v>
+        <v>-0.1649613082408905</v>
       </c>
     </row>
     <row r="287" spans="1:4">
@@ -4980,7 +4980,7 @@
         <v>9.399999618530273</v>
       </c>
       <c r="D287">
-        <v>2.416056871414185</v>
+        <v>2.714053392410278</v>
       </c>
     </row>
     <row r="288" spans="1:4">
@@ -4994,7 +4994,7 @@
         <v>-7</v>
       </c>
       <c r="D288">
-        <v>-1.486545085906982</v>
+        <v>-2.103984832763672</v>
       </c>
     </row>
     <row r="289" spans="1:4">
@@ -5008,7 +5008,7 @@
         <v>3.299999952316284</v>
       </c>
       <c r="D289">
-        <v>0.4676967859268188</v>
+        <v>0.7203270196914673</v>
       </c>
     </row>
     <row r="290" spans="1:4">
@@ -5022,7 +5022,7 @@
         <v>1.200000047683716</v>
       </c>
       <c r="D290">
-        <v>2.172136068344116</v>
+        <v>2.158162355422974</v>
       </c>
     </row>
     <row r="291" spans="1:4">
@@ -5036,7 +5036,7 @@
         <v>-0.4000000059604645</v>
       </c>
       <c r="D291">
-        <v>-0.8692978620529175</v>
+        <v>-0.4339355230331421</v>
       </c>
     </row>
     <row r="292" spans="1:4">
@@ -5050,7 +5050,7 @@
         <v>-3.299999952316284</v>
       </c>
       <c r="D292">
-        <v>-4.145553588867188</v>
+        <v>-3.831506252288818</v>
       </c>
     </row>
     <row r="293" spans="1:4">
@@ -5064,7 +5064,7 @@
         <v>7.5</v>
       </c>
       <c r="D293">
-        <v>5.046627998352051</v>
+        <v>5.228293418884277</v>
       </c>
     </row>
     <row r="294" spans="1:4">
@@ -5078,7 +5078,7 @@
         <v>-14.89999961853027</v>
       </c>
       <c r="D294">
-        <v>-9.396187782287598</v>
+        <v>-9.019972801208496</v>
       </c>
     </row>
     <row r="295" spans="1:4">
@@ -5092,7 +5092,7 @@
         <v>-1.899999976158142</v>
       </c>
       <c r="D295">
-        <v>-2.816911458969116</v>
+        <v>-2.589007139205933</v>
       </c>
     </row>
     <row r="296" spans="1:4">
@@ -5106,7 +5106,7 @@
         <v>1.700000047683716</v>
       </c>
       <c r="D296">
-        <v>0.9221224784851074</v>
+        <v>0.4417822659015656</v>
       </c>
     </row>
     <row r="297" spans="1:4">
@@ -5120,7 +5120,7 @@
         <v>-3.099999904632568</v>
       </c>
       <c r="D297">
-        <v>1.245881080627441</v>
+        <v>-3.462579011917114</v>
       </c>
     </row>
     <row r="298" spans="1:4">
@@ -5134,7 +5134,7 @@
         <v>-0.300000011920929</v>
       </c>
       <c r="D298">
-        <v>-2.982085227966309</v>
+        <v>-2.226450204849243</v>
       </c>
     </row>
     <row r="299" spans="1:4">
@@ -5148,7 +5148,7 @@
         <v>1.299999952316284</v>
       </c>
       <c r="D299">
-        <v>2.811539649963379</v>
+        <v>2.41489052772522</v>
       </c>
     </row>
     <row r="300" spans="1:4">
@@ -5162,7 +5162,7 @@
         <v>-30.5</v>
       </c>
       <c r="D300">
-        <v>-17.51640510559082</v>
+        <v>-14.87988758087158</v>
       </c>
     </row>
     <row r="301" spans="1:4">
@@ -5176,7 +5176,7 @@
         <v>4.5</v>
       </c>
       <c r="D301">
-        <v>1.481151342391968</v>
+        <v>1.436508774757385</v>
       </c>
     </row>
     <row r="302" spans="1:4">
@@ -5190,7 +5190,7 @@
         <v>-5</v>
       </c>
       <c r="D302">
-        <v>-3.184948444366455</v>
+        <v>-2.797720432281494</v>
       </c>
     </row>
     <row r="303" spans="1:4">
@@ -5204,7 +5204,7 @@
         <v>-19.29999923706055</v>
       </c>
       <c r="D303">
-        <v>-20.03518867492676</v>
+        <v>-19.38974761962891</v>
       </c>
     </row>
     <row r="304" spans="1:4">
@@ -5218,7 +5218,7 @@
         <v>0.6000000238418579</v>
       </c>
       <c r="D304">
-        <v>2.081782817840576</v>
+        <v>2.175431966781616</v>
       </c>
     </row>
     <row r="305" spans="1:4">
@@ -5232,7 +5232,7 @@
         <v>-1.100000023841858</v>
       </c>
       <c r="D305">
-        <v>-2.080916404724121</v>
+        <v>-2.375740766525269</v>
       </c>
     </row>
     <row r="306" spans="1:4">
@@ -5246,7 +5246,7 @@
         <v>2.599999904632568</v>
       </c>
       <c r="D306">
-        <v>0.8824104070663452</v>
+        <v>1.58721399307251</v>
       </c>
     </row>
     <row r="307" spans="1:4">
@@ -5260,7 +5260,7 @@
         <v>10.89999961853027</v>
       </c>
       <c r="D307">
-        <v>4.651177406311035</v>
+        <v>4.594509124755859</v>
       </c>
     </row>
     <row r="308" spans="1:4">
@@ -5274,7 +5274,7 @@
         <v>4.900000095367432</v>
       </c>
       <c r="D308">
-        <v>2.076239347457886</v>
+        <v>2.159865856170654</v>
       </c>
     </row>
   </sheetData>
